--- a/Xlsx/БД.xlsx
+++ b/Xlsx/БД.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11760"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="БД" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_EB7388BE0BB04C22A0AE207740F0A474"/>
+        <xdr:cNvPr id="3" name="ID_40D9774D3F164C828E2D9D9A7540B4AF"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -44,8 +44,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15590520" y="787400"/>
-          <a:ext cx="6372225" cy="9772650"/>
+          <a:off x="15878810" y="787400"/>
+          <a:ext cx="11553825" cy="9401175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>Файл</t>
   </si>
@@ -87,7 +87,7 @@
     <t>Картинка</t>
   </si>
   <si>
-    <t>binary_ISSI_Instabiliti_2.dat</t>
+    <t>binary_ISSI_Instabiliti_1.dat</t>
   </si>
   <si>
     <t>Laks (0)</t>
@@ -96,22 +96,19 @@
     <t>No</t>
   </si>
   <si>
-    <t>1013 years</t>
+    <t>8000 years</t>
   </si>
   <si>
     <t>Yes (frozen)</t>
   </si>
   <si>
-    <t>Сетка как предложил Марк, самый простой метод - первоначальное решение</t>
+    <t>Сетка чуть лучше чем предложил Марк (но решаю в полупространстве), самый простой метод - первоначальное решение</t>
   </si>
   <si>
-    <t>binary_ISSI_Instabiliti_3.dat</t>
+    <t>binary_ISSI_Instabiliti_2.dat</t>
   </si>
   <si>
     <t>HLL (1)</t>
-  </si>
-  <si>
-    <t>+ 37 years</t>
   </si>
 </sst>
 </file>
@@ -757,7 +754,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -767,9 +764,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -777,9 +771,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1316,16 +1307,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="31.2222222222222" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.2181818181818" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1"/>
-    <col min="4" max="4" width="14.4444444444444" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1111111111111" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="129.777777777778" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.4444444444444" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.4454545454545" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6636363636364" style="1" customWidth="1"/>
+    <col min="7" max="7" width="129.781818181818" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.4454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1"/>
@@ -1351,202 +1342,204 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:8">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4">
-        <v>2300992</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="3">
+        <v>312000</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="str">
-        <f>_xlfn.DISPIMG("ID_EB7388BE0BB04C22A0AE207740F0A474",1)</f>
-        <v>=DISPIMG("ID_EB7388BE0BB04C22A0AE207740F0A474",1)</v>
+      <c r="H3" s="4" t="str">
+        <f>_xlfn.DISPIMG("ID_40D9774D3F164C828E2D9D9A7540B4AF",1)</f>
+        <v>=DISPIMG("ID_40D9774D3F164C828E2D9D9A7540B4AF",1)</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" spans="1:8">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2300992</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3">
+        <v>312000</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:8">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:8">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:8">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:8">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" ht="40" customHeight="1" spans="1:8">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" ht="40" customHeight="1" spans="1:7">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" ht="40" customHeight="1" spans="1:7">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:7">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:7">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" ht="40" customHeight="1"/>
     <row r="22" ht="40" customHeight="1"/>
